--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_03/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_03/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>56.76</v>
+        <v>56.12</v>
       </c>
       <c r="D2" t="n">
-        <v>21.88</v>
+        <v>20.43</v>
       </c>
       <c r="E2" t="n">
-        <v>38.54</v>
+        <v>36.41</v>
       </c>
       <c r="F2" t="n">
-        <v>32.79</v>
+        <v>34.5</v>
       </c>
       <c r="G2" t="n">
-        <v>37.69</v>
+        <v>38.93</v>
       </c>
       <c r="H2" t="n">
-        <v>49.25</v>
+        <v>48.03</v>
       </c>
       <c r="I2" t="n">
-        <v>74.01000000000001</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>67.20999999999999</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>38.9</v>
+        <v>38.84</v>
       </c>
       <c r="D3" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="E3" t="n">
-        <v>0.66</v>
+        <v>0.93</v>
       </c>
       <c r="F3" t="n">
-        <v>38.79</v>
+        <v>38.58</v>
       </c>
       <c r="G3" t="n">
-        <v>38.8</v>
+        <v>38.59</v>
       </c>
       <c r="H3" t="n">
-        <v>38.81</v>
+        <v>38.66</v>
       </c>
       <c r="I3" t="n">
-        <v>38.87</v>
+        <v>39.09</v>
       </c>
       <c r="J3" t="n">
-        <v>40.06</v>
+        <v>39.61</v>
       </c>
       <c r="K3" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>7.08</v>
+        <v>7.39</v>
       </c>
       <c r="D4" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="E4" t="n">
-        <v>35.13</v>
+        <v>29.85</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>5.01</v>
+        <v>5.58</v>
       </c>
       <c r="H4" t="n">
-        <v>5.36</v>
+        <v>6.05</v>
       </c>
       <c r="I4" t="n">
-        <v>9.140000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="J4" t="n">
-        <v>12.25</v>
+        <v>11.44</v>
       </c>
       <c r="K4" t="n">
-        <v>7.25</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>92.39</v>
+        <v>76.42</v>
       </c>
       <c r="D5" t="n">
-        <v>50.35</v>
+        <v>26.79</v>
       </c>
       <c r="E5" t="n">
-        <v>54.49</v>
+        <v>35.06</v>
       </c>
       <c r="F5" t="n">
-        <v>39.41</v>
+        <v>50.47</v>
       </c>
       <c r="G5" t="n">
-        <v>58.05</v>
+        <v>58.36</v>
       </c>
       <c r="H5" t="n">
-        <v>65.43000000000001</v>
+        <v>60.09</v>
       </c>
       <c r="I5" t="n">
-        <v>147.29</v>
+        <v>93.66</v>
       </c>
       <c r="J5" t="n">
-        <v>198.51</v>
+        <v>142.98</v>
       </c>
       <c r="K5" t="n">
-        <v>159.1</v>
+        <v>92.51000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>4.28</v>
+        <v>4.41</v>
       </c>
       <c r="D6" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="E6" t="n">
-        <v>5.47</v>
+        <v>6.88</v>
       </c>
       <c r="F6" t="n">
-        <v>3.72</v>
+        <v>3.82</v>
       </c>
       <c r="G6" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="H6" t="n">
-        <v>4.28</v>
+        <v>4.39</v>
       </c>
       <c r="I6" t="n">
-        <v>4.37</v>
+        <v>4.64</v>
       </c>
       <c r="J6" t="n">
-        <v>4.91</v>
+        <v>4.97</v>
       </c>
       <c r="K6" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>
